--- a/artfynd/A 48658-2022 artfynd.xlsx
+++ b/artfynd/A 48658-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48658-2022 artfynd.xlsx
+++ b/artfynd/A 48658-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111473777</v>
+        <v>111473780</v>
       </c>
       <c r="B2" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704301.1177162804</v>
+        <v>704257</v>
       </c>
       <c r="R2" t="n">
-        <v>6573209.392206083</v>
+        <v>6573212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>asphögstubbe färsk</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,6 +774,430 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>111473777</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östra Ingarö, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>704301</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6573210</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ingarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111473778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Östra Ingarö, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>704268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6573253</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ingarö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112366368</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råuddsvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>704001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6573173</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ingarö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112366338</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råuddsvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>704001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6573173</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ingarö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Smakar bittert men saknar doft av bittermandel.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Växte under gran men fanns även tall i närheten.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48658-2022 artfynd.xlsx
+++ b/artfynd/A 48658-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111473780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111473777</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111473778</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366368</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,8 +1223,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366338</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>